--- a/2T3_manning_detail.xlsx
+++ b/2T3_manning_detail.xlsx
@@ -3,7 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Name Detail" sheetId="2" r:id="rId2"/>
+    <sheet name="All Names" sheetId="2" r:id="rId2"/>
+    <sheet name="2T3X1 Mechanics" sheetId="3" r:id="rId3"/>
+    <sheet name="2T3X7 Admin" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -14,148 +16,113 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Skill Level</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Authorized</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Current Assigned</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Current %</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Gains</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Losses</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>6 Months Out</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>6 Months %</t>
+          <t>VM Response Totals (same basis as previous answer)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9-level</t>
+          <t>Skill Level</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Current Assigned</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Current %</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Gains</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Losses</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6 Months Out</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6 Months %</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7-level</t>
+          <t>9-level</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5-level</t>
+          <t>7-level</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>150%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -165,72 +132,512 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>150%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>5-level</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>3-level</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>138%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>162%</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Breakout by AFSC Shred</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Skill Level</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Authorized Billets</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Current Names</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Gains</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6 Months Out</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9-level</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7-level</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5-level</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3-level</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9-level</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7-level</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5-level</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3-level</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Through 2026-11-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Detail tab lists current UMD-assigned names plus all 2T3 gains/losses from hail farewell.xlsx through 2026-11-30.</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2T3X1 = mechanics; 2T3X7 = admin/fleet management.</t>
         </is>
       </c>
     </row>
@@ -259,12 +666,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Skill Level</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Bucket</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -316,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARRIAGA ROEL ELIUT</t>
+          <t>MEIXNER CONRAD CLARK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -331,32 +738,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Current assigned</t>
+          <t>Current - loss</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -366,12 +773,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>ANDERSEN</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00014918GS</t>
+          <t>00014976GS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -381,14 +788,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BERGERSON MARSHAL BLAZE</t>
+          <t>ARRIAGA ROEL ELIUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -398,19 +805,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -418,7 +825,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -443,7 +850,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00015102GS</t>
+          <t>00014918GS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -453,14 +860,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRISTOW CHARLES EDWARD III</t>
+          <t>BERGERSON MARSHAL BLAZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -470,19 +877,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -490,7 +897,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -515,7 +922,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00015286GS</t>
+          <t>00015102GS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -525,14 +932,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COLLINS LILLIAN ABIGAIL</t>
+          <t>BRISTOW CHARLES EDWARD III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,14 +954,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -562,7 +969,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -587,7 +994,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00014924GS</t>
+          <t>00015286GS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -597,14 +1004,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COVELL DANIEL ALLEN</t>
+          <t>COLLINS LILLIAN ABIGAIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -614,19 +1021,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -634,7 +1041,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -659,7 +1066,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>00014947GS</t>
+          <t>00014924GS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -669,14 +1076,14 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DE LA CERDA RICARDO MIGUEL</t>
+          <t>COVELL DANIEL ALLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,19 +1093,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -706,7 +1113,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -731,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>00014949GS</t>
+          <t>00014947GS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -741,14 +1148,14 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOUBERLY SAMANTHA MORGAN</t>
+          <t>DE LA CERDA RICARDO MIGUEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,19 +1165,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -778,7 +1185,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -803,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>00015267GS</t>
+          <t>00014949GS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -813,14 +1220,14 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FITTS GAVIN WINFIELD</t>
+          <t>DOUBERLY SAMANTHA MORGAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,19 +1237,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -850,7 +1257,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -875,7 +1282,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>00015289GS</t>
+          <t>00015267GS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -885,14 +1292,14 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GREGORY DONOVYN AARON</t>
+          <t>FITTS GAVIN WINFIELD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -902,19 +1309,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -922,7 +1329,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -947,7 +1354,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>00015294GS</t>
+          <t>00015289GS</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -957,14 +1364,14 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GREGORY MIA ROSE</t>
+          <t>GREGORY DONOVYN AARON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -979,14 +1386,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -994,7 +1401,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1019,7 +1426,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>00015230GS</t>
+          <t>00015294GS</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1029,14 +1436,14 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KESCOLI CHILDS JENABAH TYLO</t>
+          <t>GREGORY MIA ROSE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1051,14 +1458,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1066,7 +1473,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1091,7 +1498,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>00015101GS</t>
+          <t>00015230GS</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1101,14 +1508,14 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KOOB AYDEN WESLEY</t>
+          <t>KESCOLI CHILDS JENABAH TYLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1118,19 +1525,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1138,7 +1545,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1163,7 +1570,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>00015195GS</t>
+          <t>00015101GS</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1173,14 +1580,14 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NINO DE RIVERA PIMENTEL JOS</t>
+          <t>KOOB AYDEN WESLEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1190,19 +1597,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1210,7 +1617,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1235,7 +1642,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>00015200GS</t>
+          <t>00015195GS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1245,14 +1652,14 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REVOIR SARINA GRACE</t>
+          <t>NINO DE RIVERA PIMENTEL JOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1262,19 +1669,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1282,7 +1689,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1307,7 +1714,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>00015093GS</t>
+          <t>00015200GS</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1317,14 +1724,14 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ROACH AIDAN DEAN</t>
+          <t>REVOIR SARINA GRACE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1334,19 +1741,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1354,7 +1761,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1379,7 +1786,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>00015197GS</t>
+          <t>00015093GS</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1389,14 +1796,14 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SALMI KATY MARIE</t>
+          <t>ROACH AIDAN DEAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1411,14 +1818,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1426,7 +1833,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1451,7 +1858,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>00015139GS</t>
+          <t>00015197GS</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1461,14 +1868,14 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THELEN COOPER SCOTT</t>
+          <t>SALMI KATY MARIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1478,19 +1885,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -1498,7 +1905,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1523,7 +1930,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>00015195GS</t>
+          <t>00015139GS</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1533,14 +1940,14 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MEIXNER CONRAD CLARK</t>
+          <t>THELEN COOPER SCOTT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1555,32 +1962,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Current assigned - loss</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1590,12 +1997,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ANDERSEN</t>
+          <t/>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>00014976GS</t>
+          <t>00015195GS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1605,7 +2012,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Current assigned; also listed as loss in hail/farewell</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -1627,12 +2034,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3-level</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1699,12 +2106,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3-level</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1771,12 +2178,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3-level</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1843,12 +2250,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3-level</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1915,12 +2322,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3-level</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1972,7 +2379,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALUPOV MAXIM</t>
+          <t>ALEXANDER JAYDEN TESLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1982,37 +2389,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Current assigned</t>
+          <t>Current - loss</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2022,12 +2429,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t/>
+          <t>Retirement/separation</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>00015285GS</t>
+          <t>00015266GS</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2037,54 +2444,54 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BATCHELDER ALEXIS MARIE</t>
+          <t>SCHWARTZ ANTHONY ISSAC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSG</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Current assigned</t>
+          <t>Current - loss</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2094,12 +2501,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t/>
+          <t>JBMDL MCGUIRE</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>00015284GS</t>
+          <t>00015198GS</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,14 +2516,14 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BINETTE THOMAS ANDRE</t>
+          <t>WILBURN JAYLON DAIJON</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2131,32 +2538,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Current assigned</t>
+          <t>Current - loss</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2166,12 +2573,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t/>
+          <t>Retirement/separation</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>00015199GS</t>
+          <t>00015081GS</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2181,14 +2588,14 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COBB BRANDON LEE</t>
+          <t>ALUPOV MAXIM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2203,14 +2610,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2218,7 +2625,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2243,7 +2650,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>00015217GS</t>
+          <t>00015285GS</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2253,19 +2660,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GARNIGAN ALEXIS DANIELLE</t>
+          <t>BATCHELDER ALEXIS MARIE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRA</t>
+          <t>SSG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2275,14 +2682,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2290,7 +2697,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2315,7 +2722,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>00015283GS</t>
+          <t>00015284GS</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2325,14 +2732,14 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HENRY MASON ANDREW</t>
+          <t>BINETTE THOMAS ANDRE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2347,14 +2754,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2362,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2387,7 +2794,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>00015055GS</t>
+          <t>00015199GS</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2397,36 +2804,36 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HOOVER KOBEY LAKE</t>
+          <t>COBB BRANDON LEE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSG</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T331</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2434,7 +2841,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2459,7 +2866,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>00015252GS</t>
+          <t>00015217GS</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2469,19 +2876,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KEIFMAN THOMAS PETER</t>
+          <t>GARNIGAN ALEXIS DANIELLE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSG</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2491,14 +2898,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2506,7 +2913,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2531,7 +2938,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>00015284GS</t>
+          <t>00015283GS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2541,14 +2948,14 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LEBLANC BOB FRANCIS JR</t>
+          <t>HENRY MASON ANDREW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2563,14 +2970,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2578,7 +2985,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2603,7 +3010,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>00015216GS</t>
+          <t>00015055GS</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2613,19 +3020,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MONTELLANO JARED JASON</t>
+          <t>HOOVER KOBEY LAKE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SRA</t>
+          <t>SSG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2635,14 +3042,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2650,7 +3057,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2675,7 +3082,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>00015232GS</t>
+          <t>00015252GS</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2685,19 +3092,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RAYMOND LUCAS ALAN</t>
+          <t>KEIFMAN THOMAS PETER</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SRA</t>
+          <t>SSG</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2707,14 +3114,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2722,7 +3129,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2747,7 +3154,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>00015190GS</t>
+          <t>00015284GS</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2757,14 +3164,14 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEREZ ERIBERTO</t>
+          <t>LEBLANC BOB FRANCIS JR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2779,14 +3186,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2794,7 +3201,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2819,7 +3226,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>00015214GS</t>
+          <t>00015216GS</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2829,19 +3236,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SANCHEZ MAKENNA KRISTYNE</t>
+          <t>MONTELLANO JARED JASON</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSG</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2851,14 +3258,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2866,7 +3273,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2891,7 +3298,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>00015265GS</t>
+          <t>00015232GS</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2901,14 +3308,14 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VALDEZ JOHN ALAN JR</t>
+          <t>RAYMOND LUCAS ALAN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2923,14 +3330,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -2938,7 +3345,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2963,7 +3370,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>00015231GS</t>
+          <t>00015190GS</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2973,19 +3380,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WAINSCOTT JACOB ETHAN</t>
+          <t>RODRIGUEZ PEREZ ERIBERTO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSG</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2995,14 +3402,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -3010,7 +3417,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3035,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>00015210GS</t>
+          <t>00015214GS</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3045,14 +3452,14 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ZUNIGA CHRISTIAN SIERRA</t>
+          <t>SANCHEZ MAKENNA KRISTYNE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3067,14 +3474,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -3082,7 +3489,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3107,7 +3514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>00015235GS</t>
+          <t>00015265GS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3117,14 +3524,14 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALEXANDER JAYDEN TESLA</t>
+          <t>VALDEZ JOHN ALAN JR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3139,32 +3546,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Current assigned - loss</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3174,12 +3581,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Retirement/separation</t>
+          <t/>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>00015266GS</t>
+          <t>00015231GS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3189,54 +3596,54 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Current assigned; also listed as loss in hail/farewell</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCHWARTZ ANTHONY ISSAC</t>
+          <t>WAINSCOTT JACOB ETHAN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SRA</t>
+          <t>SSG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Current assigned - loss</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t/>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3246,12 +3653,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>JBMDL MCGUIRE</t>
+          <t/>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>00015198GS</t>
+          <t>00015210GS</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3261,19 +3668,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Current assigned; also listed as loss in hail/farewell</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WILBURN JAYLON DAIJON</t>
+          <t>ZUNIGA CHRISTIAN SIERRA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SRA</t>
+          <t>SSG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3283,32 +3690,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Current assigned - loss</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3318,12 +3725,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Retirement/separation</t>
+          <t/>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>00015081GS</t>
+          <t>00015235GS</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3333,7 +3740,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Current assigned; also listed as loss in hail/farewell</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3762,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>5-level</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3427,14 +3834,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -3442,7 +3849,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Not in UMD current list</t>
+          <t>Not in detail current list</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3499,14 +3906,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -3514,7 +3921,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Not in UMD current list</t>
+          <t>Not in detail current list</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3556,7 +3963,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FANT JONTAE ARLEN</t>
+          <t>LOPEZ DYLAN JOSEPH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3566,19 +3973,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2T357</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -3586,7 +3993,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Not in UMD current list</t>
+          <t>Not in detail current list</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3596,7 +4003,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3611,7 +4018,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>LGRVA</t>
+          <t>LGRVF</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3628,37 +4035,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LOPEZ DYLAN JOSEPH</t>
+          <t>WALSH KYLE J</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSG</t>
+          <t>TSG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2T351</t>
+          <t>2T371</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2T3X1 - Mechanic</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5-level</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Current - loss</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Not in UMD current list</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3668,7 +4075,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3683,17 +4090,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>LGRVF</t>
+          <t>00015293GS</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>hail farewell.xlsx</t>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Retirement/separation; listed here for visibility</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
         </is>
       </c>
     </row>
@@ -3715,14 +4122,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -3730,7 +4137,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3765,7 +4172,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -3787,14 +4194,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -3802,7 +4209,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3837,7 +4244,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -3859,14 +4266,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -3874,7 +4281,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3909,7 +4316,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -3931,14 +4338,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -3946,7 +4353,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3981,7 +4388,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -4003,14 +4410,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -4018,7 +4425,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4053,7 +4460,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -4075,14 +4482,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -4090,7 +4497,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4125,7 +4532,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -4147,14 +4554,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -4162,7 +4569,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4197,7 +4604,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
@@ -4219,14 +4626,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>Current assigned</t>
@@ -4234,7 +4641,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - UMD</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4269,54 +4676,54 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Counted from Control Skill Level 2 (Array)</t>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WALSH KYLE J</t>
+          <t>DEL ANGEL ERIKA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TSG</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2T371</t>
+          <t>2T337</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2T3X7 - Admin/Fleet</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7-level</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Current assigned - loss</t>
+          <t>Current roster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes - roster</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4326,92 +4733,5794 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Retirement/separation</t>
+          <t/>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>00015293GS</t>
+          <t>0015067GS</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>Export (15).xlsx / AirmanGuardian</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Current assigned; also listed as loss in hail/farewell</t>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>EASON ZAVIA CHANEL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0044310GS</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LYNN GRACE ANNE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AMN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0044311GS</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MURRAY TAHJE WYSHAUN</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AMN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0044310GS</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NANA ANISSATOU</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0015297GS</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>YAO EDOH EUGENE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0044312GS</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>YOUNG NINA LI</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0044312GS</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FANT JONTAE ARLEN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2T357</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0015058GS</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ACHTERHOF MICHAEL JAMES</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0015058GS</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SCHEEL JARED WAYNE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0015050GS</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SUTTON ALYSSA KRISTENE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0014871GS</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>GILBERT GREGORY</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>MSG</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>2T377</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Gain</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>31 LOGISTICS READINES SQUADRON</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>MINOT</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>LGRVA</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>hail farewell.xlsx</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>AFSC</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Skill Level</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Counted Current</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Counted 6 Months Out</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Effective Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Position/Org</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEIXNER CONRAD CLARK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ANDERSEN</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00014976GS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ARRIAGA ROEL ELIUT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00014918GS</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BERGERSON MARSHAL BLAZE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00015102GS</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRISTOW CHARLES EDWARD III</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00015286GS</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>COLLINS LILLIAN ABIGAIL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00014924GS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COVELL DANIEL ALLEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00014947GS</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DE LA CERDA RICARDO MIGUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00014949GS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DOUBERLY SAMANTHA MORGAN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00015267GS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FITTS GAVIN WINFIELD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00015289GS</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GREGORY DONOVYN AARON</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00015294GS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GREGORY MIA ROSE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00015230GS</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KESCOLI CHILDS JENABAH TYLO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00015101GS</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KOOB AYDEN WESLEY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00015195GS</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NINO DE RIVERA PIMENTEL JOS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00015200GS</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REVOIR SARINA GRACE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00015093GS</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ROACH AIDAN DEAN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00015197GS</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SALMI KATY MARIE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>00015139GS</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>THELEN COOPER SCOTT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>00015195GS</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DALTON NATHANIEL JOSEPH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>36 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>LGRV</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HUGHESBOGGS QUEST NAIM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>346 TRAINING SQUADRON (OL AFS)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OTTOSEN DYLAN JOEL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>346 TRAINING SQUADRON (OL AFS)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ GABRIEL ANDRES</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>346 TRAINING SQUADRON (OL AFS)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RUIZ ROBERTO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>346 TRAINING SQUADRON (OL AFS)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ALEXANDER JAYDEN TESLA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>00015266GS</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SCHWARTZ ANTHONY ISSAC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>JBMDL MCGUIRE</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>00015198GS</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WILBURN JAYLON DAIJON</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>00015081GS</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ALUPOV MAXIM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>00015285GS</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BATCHELDER ALEXIS MARIE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>00015284GS</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BINETTE THOMAS ANDRE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>00015199GS</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>COBB BRANDON LEE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2T331</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>00015217GS</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GARNIGAN ALEXIS DANIELLE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>00015283GS</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HENRY MASON ANDREW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>00015055GS</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HOOVER KOBEY LAKE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>00015252GS</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KEIFMAN THOMAS PETER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>00015284GS</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LEBLANC BOB FRANCIS JR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>00015216GS</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MONTELLANO JARED JASON</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>00015232GS</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RAYMOND LUCAS ALAN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>00015190GS</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PEREZ ERIBERTO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>00015214GS</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SANCHEZ MAKENNA KRISTYNE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>00015265GS</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VALDEZ JOHN ALAN JR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>00015231GS</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WAINSCOTT JACOB ETHAN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>00015210GS</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZUNIGA CHRISTIAN SIERRA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>00015235GS</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HILDEBRAND CONNOR J</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>86 VEHICLE READINESS SQUADRON</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LGRVS</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Inbound by RNLTD within 6-month window</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AMORIM ANTHONY JAMES</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Not in detail current list</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>LGRVC</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Retirement/separation; listed here for visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BUZZARD MANDA KAY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Not in detail current list</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>JB LANGLEY-EUSTIS</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>LGRVC</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>PCS out; listed here for visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LOPEZ DYLAN JOSEPH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Not in detail current list</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>LGRVF</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Retirement/separation; listed here for visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WALSH KYLE J</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>00015293GS</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ADAMS JOSHUA A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>00015264GS</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AGUON RAYMOND VILLAGOMEZ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>00015292GS</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BROWNING CADE MITCH</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>00014903GS</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ELDRIDGE WILLIAM ZACHARY</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2T351</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>00015099GS</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>HUCKABEE ADAM THOMAS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>00015194GS</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HYDE DYLAN JACOB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>00015047GS</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ROHN ERIC JOHN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>00015202GS</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VOJSLAVEK WILLIAM JAKE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2T371</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Current assigned</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes - UMD</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>00014932GS</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AFMAA UMD Position</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>AFSC</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Skill Level</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Counted Current</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Counted 6 Months Out</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Effective Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Position/Org</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DEL ANGEL ERIKA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0015067GS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EASON ZAVIA CHANEL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0044310GS</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LYNN GRACE ANNE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AMN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0044311GS</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MURRAY TAHJE WYSHAUN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AMN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0044310GS</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NANA ANISSATOU</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0015297GS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>YAO EDOH EUGENE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0044312GS</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>YOUNG NINA LI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2T337</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0044312GS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FANT JONTAE ARLEN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2T357</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Current - loss</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Retirement/separation</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0015058GS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet; also listed as loss in hail/farewell</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ACHTERHOF MICHAEL JAMES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TSG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0015058GS</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCHEEL JARED WAYNE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0015050GS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUTTON ALYSSA KRISTENE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Current roster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes - roster</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0014871GS</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Export (15).xlsx / AirmanGuardian</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GILBERT GREGORY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2T377</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>31 LOGISTICS READINES SQUADRON</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>MINOT</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LGRVA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>hail farewell.xlsx</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Inbound by RNLTD within 6-month window</t>
         </is>

--- a/2T3_manning_detail.xlsx
+++ b/2T3_manning_detail.xlsx
@@ -16,628 +16,208 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>VM Response Totals (same basis as previous answer)</t>
+          <t>Email Table - 2T3X1 Mechanic / 2T3X7 Admin-Fleet Breakout</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AFSC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Skill Level</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Authorized</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Current Assigned</t>
+          <t>Current Manning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Current %</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Gains</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Losses</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>6 Months Out</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>6 Months %</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>9-level</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1 authorized / 0 assigned - 0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1 authorized / 0 assigned - 0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>7-level</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6 authorized / 9 assigned - 150%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>150%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>150%</t>
+          <t>6 authorized / 8 assigned - 133%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>5-level</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41 authorized / 19 assigned - 46%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>41 authorized / 15 assigned - 37%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2T3X1 - Mechanic</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>3-level</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13 authorized / 18 assigned - 138%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>138%</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>162%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>13 authorized / 21 assigned - 162%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7-level</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 authorized / 3 assigned - 100%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3 authorized / 4 assigned - 133%</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Breakout by AFSC Shred</t>
+          <t>2T3X7 - Admin/Fleet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5-level</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1 authorized / 1 assigned - 100%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1 authorized / 0 assigned - 0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>2T3X7 - Admin/Fleet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Skill Level</t>
+          <t>3-level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Authorized Billets</t>
+          <t>5 authorized / 7 assigned - 140%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Current Names</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Gains</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Losses</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6 Months Out</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2T3X1 - Mechanic</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>9-level</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+          <t>5 authorized / 7 assigned - 140%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2T3X1 - Mechanic</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7-level</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
+          <t>X1 authorized billets from AFMAA UMD Position. X7 authorized billets from visible X7 duty positions in AirmanGuardian because they were not represented as AD ENL X7 in the AFMAA position tab.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2T3X1 - Mechanic</t>
+          <t>Movement Window</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5-level</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2T3X1 - Mechanic</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2T3X7 - Admin/Fleet</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>9-level</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2T3X7 - Admin/Fleet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7-level</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2T3X7 - Admin/Fleet</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5-level</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2T3X7 - Admin/Fleet</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3-level</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>No AD ENL X7 billet found in UMD; current X7 names pulled from AirmanGuardian roster</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Through 2026-11-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2T3X1 = mechanics; 2T3X7 = admin/fleet management.</t>
+          <t>Through 2026-11-30 from hail farewell.xlsx</t>
         </is>
       </c>
     </row>
@@ -753,7 +333,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -783,12 +363,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -825,7 +405,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -855,12 +435,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -897,7 +477,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,12 +507,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -969,7 +549,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -999,12 +579,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1041,7 +621,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1071,12 +651,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1113,7 +693,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1143,12 +723,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1185,7 +765,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1215,12 +795,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1257,7 +837,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1287,12 +867,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1329,7 +909,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1359,12 +939,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1401,7 +981,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1431,12 +1011,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1053,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1503,12 +1083,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1125,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1575,12 +1155,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1197,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1647,12 +1227,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1269,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1719,12 +1299,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1341,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1791,12 +1371,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1413,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1863,12 +1443,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1485,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1935,12 +1515,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1537,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1977,7 +1557,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2007,12 +1587,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -2084,7 +1664,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -2156,7 +1736,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +1808,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -2300,7 +1880,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -2372,7 +1952,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -2409,7 +1989,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2439,12 +2019,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2061,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2511,12 +2091,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2133,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2583,12 +2163,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2205,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2655,12 +2235,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2277,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2727,12 +2307,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2349,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2799,12 +2379,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2421,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2871,12 +2451,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2493,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2943,12 +2523,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2565,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3015,12 +2595,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3057,7 +2637,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3087,12 +2667,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3129,7 +2709,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3159,12 +2739,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3201,7 +2781,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3231,12 +2811,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3273,7 +2853,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3303,12 +2883,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3345,7 +2925,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3375,12 +2955,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3417,7 +2997,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3447,12 +3027,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3069,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3519,12 +3099,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3591,12 +3171,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3213,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3663,12 +3243,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3285,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3735,12 +3315,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3392,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3429,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Not in detail current list</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3884,7 +3464,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Retirement/separation; listed here for visibility</t>
+          <t>Retirement/separation</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3501,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Not in detail current list</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3956,7 +3536,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PCS out; listed here for visibility</t>
+          <t>PCS out</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3573,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Not in detail current list</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4028,7 +3608,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Retirement/separation; listed here for visibility</t>
+          <t>Retirement/separation</t>
         </is>
       </c>
     </row>
@@ -4065,7 +3645,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4095,12 +3675,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -4137,7 +3717,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4167,12 +3747,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4209,7 +3789,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4239,12 +3819,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4281,7 +3861,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4311,12 +3891,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4353,7 +3933,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4383,12 +3963,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4005,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4455,12 +4035,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4077,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4527,12 +4107,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4149,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4599,12 +4179,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4221,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4671,12 +4251,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4288,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4743,12 +4323,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -4780,12 +4360,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4815,12 +4395,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4432,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4887,12 +4467,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4504,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4959,12 +4539,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4576,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5031,12 +4611,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -5068,12 +4648,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5103,12 +4683,12 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -5140,12 +4720,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5175,12 +4755,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -5217,7 +4797,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5247,12 +4827,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet; also listed as loss in hail/farewell</t>
+          <t>X7 billet/current count from duty position roster; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -5284,12 +4864,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5319,12 +4899,12 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -5356,12 +4936,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5391,12 +4971,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5008,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5463,12 +5043,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5120,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5236,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5686,12 +5266,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5308,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5758,12 +5338,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5830,12 +5410,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5452,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5902,12 +5482,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5524,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5974,12 +5554,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6016,7 +5596,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6046,12 +5626,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6088,7 +5668,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6118,12 +5698,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6160,7 +5740,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6190,12 +5770,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6232,7 +5812,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6262,12 +5842,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6304,7 +5884,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6334,12 +5914,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6376,7 +5956,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6406,12 +5986,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6028,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6478,12 +6058,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6100,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6550,12 +6130,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6172,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6622,12 +6202,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6244,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6694,12 +6274,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6316,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6766,12 +6346,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6388,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6838,12 +6418,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6440,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2T331</t>
+          <t>2T351</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6880,7 +6460,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6910,12 +6490,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6567,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -7059,7 +6639,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -7131,7 +6711,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -7203,7 +6783,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -7275,7 +6855,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -7312,7 +6892,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7342,12 +6922,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -7384,7 +6964,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7414,12 +6994,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7036,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7486,12 +7066,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7108,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -7558,12 +7138,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7180,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -7630,12 +7210,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -7702,12 +7282,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7324,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -7774,12 +7354,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7396,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7846,12 +7426,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7468,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7918,12 +7498,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7540,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -7990,12 +7570,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8032,7 +7612,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -8062,12 +7642,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8104,7 +7684,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -8134,12 +7714,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8176,7 +7756,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -8206,12 +7786,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8248,7 +7828,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -8278,12 +7858,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8320,7 +7900,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -8350,12 +7930,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8392,7 +7972,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -8422,12 +8002,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8044,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -8494,12 +8074,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8116,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -8566,12 +8146,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8188,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -8638,12 +8218,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8295,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8332,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Not in detail current list</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -8787,7 +8367,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Retirement/separation; listed here for visibility</t>
+          <t>Retirement/separation</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8404,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Not in detail current list</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -8859,7 +8439,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PCS out; listed here for visibility</t>
+          <t>PCS out</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8476,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Not in detail current list</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8931,7 +8511,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Retirement/separation; listed here for visibility</t>
+          <t>Retirement/separation</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8548,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8998,12 +8578,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC; also listed as loss in hail/farewell</t>
+          <t>X1 billet/current count from UMD position sheet; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -9040,7 +8620,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -9070,12 +8650,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9112,7 +8692,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -9142,12 +8722,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9184,7 +8764,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -9214,12 +8794,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9256,7 +8836,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -9286,12 +8866,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9328,7 +8908,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9358,12 +8938,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9400,7 +8980,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -9430,12 +9010,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9052,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9502,12 +9082,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9124,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes - UMD</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9574,12 +9154,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AFMAA UMD Position</t>
+          <t>AFMAA UMD Position</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Counted from UMD Control Skill Level 2 (Array); type from billet AFSC</t>
+          <t>X1 billet/current count from UMD position sheet</t>
         </is>
       </c>
     </row>
@@ -9690,12 +9270,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -9725,12 +9305,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -9762,12 +9342,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -9797,12 +9377,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9414,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -9869,12 +9449,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -9906,12 +9486,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -9941,12 +9521,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9558,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10013,12 +9593,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -10050,12 +9630,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10085,12 +9665,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -10122,12 +9702,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10157,12 +9737,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -10199,7 +9779,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10229,12 +9809,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet; also listed as loss in hail/farewell</t>
+          <t>X7 billet/current count from duty position roster; also listed as loss</t>
         </is>
       </c>
     </row>
@@ -10266,12 +9846,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10301,12 +9881,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -10338,12 +9918,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10373,12 +9953,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -10410,12 +9990,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Current roster</t>
+          <t>Current assigned</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes - roster</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10445,12 +10025,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Export (15).xlsx / AirmanGuardian</t>
+          <t>AirmanGuardian</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X7/admin current roster name; no AD ENL X7 billet found in UMD position sheet</t>
+          <t>X7 billet/current count from duty position roster</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10102,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inbound by RNLTD within 6-month window</t>
+          <t>Inbound by RNLTD through 2026-11-30</t>
         </is>
       </c>
     </row>
